--- a/docs/holdtiming/results/YZ그룹_분기예측.xlsx
+++ b/docs/holdtiming/results/YZ그룹_분기예측.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기_패널" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="베타_알파" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9셀_전이" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -104,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -123,11 +126,22 @@
         <color rgb="FF37474F"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDBDBD"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDBDBD"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FFBDBDBD"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +183,42 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1494,4 +1544,825 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>9셀(변동성 3 × 전분기 수익률 3) → 다음 분기 수익률 3분할</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>분기 14개 · 셀-분기 관측 125개 · 변동성 축 하나만 보던 앞 검정에, 전분기 수익률을 함께 조건에 넣은 것(=변동성으로 조건부한 모멘텀/반전)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>① 통합 — 9셀이 다음 분기 어디로 가나 (%). 무작위면 각 33.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>변동성</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>전분기 수익</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>분기수</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>평균종목</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>순위백분위</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>37.07142857142857</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>0.3621145527131203</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>0.2525037785127389</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>0.3853816687741408</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>0.4918092662045903</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>13.78571428571429</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0.3829871983758539</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>0.2455020644621485</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>0.3715107371619976</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>0.5165471690413012</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>16.28571428571428</v>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>0.381878124210057</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0.2461880626376425</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>0.3719338131523006</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0.5153359590705595</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>20.21428571428572</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>0.3321685821891339</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>0.3054112455258783</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>0.3624201722849878</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>0.4846002478873672</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>22.07142857142857</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0.330062388545553</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>0.321381351930551</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0.348556259523896</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.4904441505333949</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>0.354044771104571</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0.2887325231305552</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.3572227057648737</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>0.4941591577026377</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>10.46153846153846</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>0.2830830557074901</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0.4204540557481734</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.2964628885443365</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>0.4870690618271913</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>30.78571428571428</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>0.2609409610104242</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>0.5098482740679136</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.2292107649216622</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>0.5214860595918006</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>0.3200885761154733</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>0.3922113064848045</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>0.2877001173997222</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>0.5060483126881633</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>② 셀별 부호검정 — 분기를 단위로 (종목이 아니다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>셀</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>순위&gt;0.5</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>평균 순위백분위</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>부호검정 p</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>변동성 고 · 전분기수익 상</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="n">
+        <v>0.4918092662045903</v>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>변동성 고 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="n">
+        <v>0.516547169041301</v>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>변동성 고 · 전분기수익 하</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>0.5153359590705594</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 상</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>0.4846002478873672</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="n">
+        <v>0.4904441505333949</v>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>0.1795654296875</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 하</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="n">
+        <v>0.4941591577026377</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>변동성 저 · 전분기수익 상</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="n">
+        <v>0.4870690618271913</v>
+      </c>
+      <c r="E26" s="27" t="n">
+        <v>0.5810546875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>변동성 저 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>0.5214860595918006</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>변동성 저 · 전분기수익 하</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>0.5060483126881633</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>★ **9셀 어디에도 예측력이 없다.** 평균 순위백분위가 48.5~52.1% 로 전부 50% 근처이고, 부호검정 p 는 0.18~1.00 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   셀이 9개라 다중비교다 — 본페로니 임계 p &lt; 0.0056. **근처에 온 셀조차 없다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>★ **전분기 수익률 축은 아무 정보도 없다.** 같은 변동성 안에서 상/중/하의 다음 분기 분포가 거의 같다(예: 고변동에서 '상' 36.2 / '중' 38.3 / '하' 38.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **모멘텀도 반전도 없다.** 변동성으로 조건을 걸어도 마찬가지다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>③ ★ 그런데 '방향' 이 아니라 '산포' 는 아주 강하게 예측한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>변동성</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 '중간' 비율</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>'중간' &lt; 33.3% 인 분기</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>'중간' &gt; 33.3% 인 분기</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>p(치우침)</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 수익률 sd</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>sd / 시장sd</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>0.2423371309379249</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>0/14</t>
+        </is>
+      </c>
+      <c r="F38" s="28" t="n">
+        <v>0.0001220703125</v>
+      </c>
+      <c r="G38" s="23" t="n">
+        <v>0.3591701874901823</v>
+      </c>
+      <c r="H38" s="11" t="n">
+        <v>1.241659688105479</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C39" s="23" t="n">
+        <v>0.3025511806199361</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+      <c r="F39" s="28" t="n">
+        <v>0.012939453125</v>
+      </c>
+      <c r="G39" s="23" t="n">
+        <v>0.2505778672840408</v>
+      </c>
+      <c r="H39" s="11" t="n">
+        <v>0.9545662061401605</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>0.4544587523063709</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>0/14</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+      <c r="F40" s="28" t="n">
+        <v>0.0001220703125</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>0.1465956287972339</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>0.5541064528533126</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   무작위면 '중간' 비율이 33.3% 여야 한다. 실측은 **고 24.2% / 중 30.3% / 저 45.4%** 다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **고 그룹은 14/14 분기에서 33.3% 미만, 저 그룹은 14/14 분기에서 초과** (각 p = 0.0001). 예외가 한 분기도 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   다음 분기 수익률 표준편차도 **고 그룹이 저 그룹의 2.26배**이고, 13/14 분기에서 그렇다 (p = 0.0018).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>⇒ **변동성 그룹은 다음 분기에 '어디로 갈지' 는 못 맞히지만 '얼마나 멀리 갈지' 는 아주 잘 맞힌다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   고변동 그룹은 다음 분기에도 양 끝(상·하)으로 벌어지고, 저변동 그룹은 가운데로 몰린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 이건 놀라운 결과가 아니다 — 변동성 지속성(§10-5)을 '다음 분기 수익률의 퍼짐' 이라는 실용적 형태로 다시 말한 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>⇒ **쓸모의 방향이 정해진다.** 이 그룹은 종목 고르기(알파)가 아니라 **위험 예산·포지션 사이징**에 쓰는 것이 맞다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   같은 금액을 넣어도 고 그룹은 저 그룹의 2.26배로 흔들린다는 뜻이니까.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 다만 '어느 쪽으로' 흔들릴지는 이 표가 말해주지 않는다. 손실 쪽도 그만큼 넓다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/holdtiming/results/YZ그룹_분기예측.xlsx
+++ b/docs/holdtiming/results/YZ그룹_분기예측.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,6 +93,11 @@
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF6D4C41"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -141,7 +146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -192,16 +197,16 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -210,6 +215,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -1552,7 +1558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1579,509 +1585,532 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>분할은 **균등 3분할(1/3 : 1/3 : 1/3)** 이다 — 3:4:3 이 아니다. 두 축 모두 `rank(pct) ≤ 1/3, ≤ 2/3` 로 자른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   실측 축 비율 — 변동성 저 33.2% / 중 33.3% / 고 33.6%   ·   수익률 하 33.1% / 중 33.3% / 상 33.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   분기당 판정 종목 193~206종목 (중앙 201).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>⚠ **축은 균등한데 9셀은 전혀 균등하지 않다.** 두 축이 독립이면 각 셀이 11.1% 여야 하는데 실제는 4.9%~18.5% 다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   변동성이 큰 종목이 수익률 극단으로도 가기 때문이다. **셀 크기의 불균등 자체가 아래 ② 산포 결과와 같은 현상이다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>① 통합 — 9셀이 다음 분기 어디로 가나 (%). 무작위면 각 33.3</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>변동성</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>전분기 수익</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>n합계</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>전체 대비</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>분기수</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>평균종목</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>n평균</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>n최소</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>n최대</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>순위백분위</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>고</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C13" s="19" t="n">
+        <v>519</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>0.1854233654876742</v>
+      </c>
+      <c r="E13" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="F13" s="21" t="n">
         <v>37.07142857142857</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="G13" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="I13" s="20" t="n">
         <v>0.3621145527131203</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="J13" s="20" t="n">
         <v>0.2525037785127389</v>
       </c>
-      <c r="G7" s="21" t="n">
+      <c r="K13" s="20" t="n">
         <v>0.3853816687741408</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="L13" s="20" t="n">
         <v>0.4918092662045903</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>고</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C14" s="19" t="n">
+        <v>193</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>0.06895319757056091</v>
+      </c>
+      <c r="E14" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="F14" s="21" t="n">
         <v>13.78571428571429</v>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="G14" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="I14" s="20" t="n">
         <v>0.3829871983758539</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="J14" s="20" t="n">
         <v>0.2455020644621485</v>
       </c>
-      <c r="G8" s="21" t="n">
+      <c r="K14" s="20" t="n">
         <v>0.3715107371619976</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="L14" s="20" t="n">
         <v>0.5165471690413012</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>고</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C15" s="7" t="n">
+        <v>228</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>0.08145766345123258</v>
+      </c>
+      <c r="E15" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="F15" s="23" t="n">
         <v>16.28571428571428</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="G15" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="I15" s="22" t="n">
         <v>0.381878124210057</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="J15" s="22" t="n">
         <v>0.2461880626376425</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="K15" s="22" t="n">
         <v>0.3719338131523006</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="L15" s="22" t="n">
         <v>0.5153359590705595</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C16" s="19" t="n">
+        <v>283</v>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>0.1011075384065738</v>
+      </c>
+      <c r="E16" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="F16" s="21" t="n">
         <v>20.21428571428572</v>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="G16" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I16" s="20" t="n">
         <v>0.3321685821891339</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="J16" s="20" t="n">
         <v>0.3054112455258783</v>
       </c>
-      <c r="G10" s="21" t="n">
+      <c r="K16" s="20" t="n">
         <v>0.3624201722849878</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="L16" s="20" t="n">
         <v>0.4846002478873672</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C17" s="19" t="n">
+        <v>309</v>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>0.1103965702036442</v>
+      </c>
+      <c r="E17" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="F17" s="21" t="n">
         <v>22.07142857142857</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="G17" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I17" s="20" t="n">
         <v>0.330062388545553</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="J17" s="20" t="n">
         <v>0.321381351930551</v>
       </c>
-      <c r="G11" s="21" t="n">
+      <c r="K17" s="20" t="n">
         <v>0.348556259523896</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="L17" s="20" t="n">
         <v>0.4904441505333949</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C18" s="7" t="n">
+        <v>340</v>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>0.1214719542693819</v>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="F18" s="23" t="n">
         <v>24.28571428571428</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="G18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="22" t="n">
         <v>0.354044771104571</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="J18" s="22" t="n">
         <v>0.2887325231305552</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="K18" s="22" t="n">
         <v>0.3572227057648737</v>
       </c>
-      <c r="H12" s="23" t="n">
+      <c r="L18" s="22" t="n">
         <v>0.4941591577026377</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>저</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C19" s="19" t="n">
+        <v>136</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>0.04858878170775277</v>
+      </c>
+      <c r="E19" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="F19" s="21" t="n">
         <v>10.46153846153846</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="G19" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="I19" s="20" t="n">
         <v>0.2830830557074901</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="J19" s="20" t="n">
         <v>0.4204540557481734</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="K19" s="20" t="n">
         <v>0.2964628885443365</v>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="L19" s="20" t="n">
         <v>0.4870690618271913</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>저</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C20" s="19" t="n">
+        <v>431</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>0.1539835655591283</v>
+      </c>
+      <c r="E20" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="F20" s="21" t="n">
         <v>30.78571428571428</v>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="G20" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="I20" s="20" t="n">
         <v>0.2609409610104242</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="J20" s="20" t="n">
         <v>0.5098482740679136</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="K20" s="20" t="n">
         <v>0.2292107649216622</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="L20" s="20" t="n">
         <v>0.5214860595918006</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>저</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C21" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>0.1286173633440514</v>
+      </c>
+      <c r="E21" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="F21" s="23" t="n">
         <v>25.71428571428572</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="G21" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="I21" s="22" t="n">
         <v>0.3200885761154733</v>
       </c>
-      <c r="F15" s="23" t="n">
+      <c r="J21" s="22" t="n">
         <v>0.3922113064848045</v>
       </c>
-      <c r="G15" s="23" t="n">
+      <c r="K21" s="22" t="n">
         <v>0.2877001173997222</v>
       </c>
-      <c r="H15" s="23" t="n">
+      <c r="L21" s="22" t="n">
         <v>0.5060483126881633</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   n합계 = 14분기 누적 셀-분기 종목 수 (총 2,799). ⚠ 셀-분기 표본이 5종목 미만이면 그 분기는 제외했다 — 실측 최소가 2종목까지 내려가는데 그런 분기의 비율은 잡음이다(저·상 이 1개 분기 빠져 13분기).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>② 셀별 부호검정 — 분기를 단위로 (종목이 아니다)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>셀</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>분기</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>순위&gt;0.5</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>평균 순위백분위</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>부호검정 p</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>변동성 고 · 전분기수익 상</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>6/14</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="n">
-        <v>0.4918092662045903</v>
-      </c>
-      <c r="E20" s="27" t="n">
-        <v>0.79052734375</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>변동성 고 · 전분기수익 중</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>8/14</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="n">
-        <v>0.516547169041301</v>
-      </c>
-      <c r="E21" s="27" t="n">
-        <v>0.79052734375</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>변동성 고 · 전분기수익 하</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>7/14</t>
-        </is>
-      </c>
-      <c r="D22" s="23" t="n">
-        <v>0.5153359590705594</v>
-      </c>
-      <c r="E22" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="26" t="inlineStr">
-        <is>
-          <t>변동성 중 · 전분기수익 상</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>6/14</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>0.4846002478873672</v>
-      </c>
-      <c r="E23" s="27" t="n">
-        <v>0.79052734375</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="26" t="inlineStr">
-        <is>
-          <t>변동성 중 · 전분기수익 중</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>4/14</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="n">
-        <v>0.4904441505333949</v>
-      </c>
-      <c r="E24" s="27" t="n">
-        <v>0.1795654296875</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>변동성 중 · 전분기수익 하</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>7/14</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="n">
-        <v>0.4941591577026377</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="26" t="inlineStr">
-        <is>
-          <t>변동성 저 · 전분기수익 상</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>5/13</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="n">
-        <v>0.4870690618271913</v>
-      </c>
-      <c r="E26" s="27" t="n">
-        <v>0.5810546875</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>변동성 저 · 전분기수익 중</t>
         </is>
       </c>
       <c r="B27" s="19" t="n">
@@ -2089,274 +2118,421 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
+          <t>6/14</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>0.4918092662045903</v>
+      </c>
+      <c r="E27" s="28" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>변동성 고 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
           <t>8/14</t>
         </is>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D28" s="20" t="n">
+        <v>0.516547169041301</v>
+      </c>
+      <c r="E28" s="28" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>변동성 고 · 전분기수익 하</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>0.5153359590705594</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="27" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 상</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="n">
+        <v>0.4846002478873672</v>
+      </c>
+      <c r="E30" s="28" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>0.4904441505333949</v>
+      </c>
+      <c r="E31" s="28" t="n">
+        <v>0.1795654296875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 하</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>0.4941591577026377</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>변동성 저 · 전분기수익 상</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="n">
+        <v>0.4870690618271913</v>
+      </c>
+      <c r="E33" s="28" t="n">
+        <v>0.5810546875</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>변동성 저 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="n">
         <v>0.5214860595918006</v>
       </c>
-      <c r="E27" s="27" t="n">
+      <c r="E34" s="28" t="n">
         <v>0.79052734375</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>변동성 저 · 전분기수익 하</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n">
+      <c r="B35" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>7/14</t>
         </is>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D35" s="22" t="n">
         <v>0.5060483126881633</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E35" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>★ **9셀 어디에도 예측력이 없다.** 평균 순위백분위가 48.5~52.1% 로 전부 50% 근처이고, 부호검정 p 는 0.18~1.00 이다.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">   셀이 9개라 다중비교다 — 본페로니 임계 p &lt; 0.0056. **근처에 온 셀조차 없다.**</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>★ **전분기 수익률 축은 아무 정보도 없다.** 같은 변동성 안에서 상/중/하의 다음 분기 분포가 거의 같다(예: 고변동에서 '상' 36.2 / '중' 38.3 / '하' 38.2).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">   ⇒ **모멘텀도 반전도 없다.** 변동성으로 조건을 걸어도 마찬가지다.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>③ ★ 그런데 '방향' 이 아니라 '산포' 는 아주 강하게 예측한다</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>변동성</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>분기</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>다음분기 '중간' 비율</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>'중간' &lt; 33.3% 인 분기</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>'중간' &gt; 33.3% 인 분기</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>p(치우침)</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
         <is>
           <t>다음분기 수익률 sd</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>sd / 시장sd</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>고</t>
         </is>
       </c>
-      <c r="B38" s="7" t="n">
+      <c r="B45" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C38" s="23" t="n">
+      <c r="C45" s="22" t="n">
         <v>0.2423371309379249</v>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>14/14</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>0/14</t>
         </is>
       </c>
-      <c r="F38" s="28" t="n">
+      <c r="F45" s="29" t="n">
         <v>0.0001220703125</v>
       </c>
-      <c r="G38" s="23" t="n">
+      <c r="G45" s="22" t="n">
         <v>0.3591701874901823</v>
       </c>
-      <c r="H38" s="11" t="n">
+      <c r="H45" s="11" t="n">
         <v>1.241659688105479</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="B39" s="7" t="n">
+      <c r="B46" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C39" s="23" t="n">
+      <c r="C46" s="22" t="n">
         <v>0.3025511806199361</v>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>10/14</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>2/14</t>
         </is>
       </c>
-      <c r="F39" s="28" t="n">
+      <c r="F46" s="29" t="n">
         <v>0.012939453125</v>
       </c>
-      <c r="G39" s="23" t="n">
+      <c r="G46" s="22" t="n">
         <v>0.2505778672840408</v>
       </c>
-      <c r="H39" s="11" t="n">
+      <c r="H46" s="11" t="n">
         <v>0.9545662061401605</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>저</t>
         </is>
       </c>
-      <c r="B40" s="7" t="n">
+      <c r="B47" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="C40" s="23" t="n">
+      <c r="C47" s="22" t="n">
         <v>0.4544587523063709</v>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>0/14</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>14/14</t>
         </is>
       </c>
-      <c r="F40" s="28" t="n">
+      <c r="F47" s="29" t="n">
         <v>0.0001220703125</v>
       </c>
-      <c r="G40" s="23" t="n">
+      <c r="G47" s="22" t="n">
         <v>0.1465956287972339</v>
       </c>
-      <c r="H40" s="11" t="n">
+      <c r="H47" s="11" t="n">
         <v>0.5541064528533126</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">   무작위면 '중간' 비율이 33.3% 여야 한다. 실측은 **고 24.2% / 중 30.3% / 저 45.4%** 다.</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   **고 그룹은 14/14 분기에서 33.3% 미만, 저 그룹은 14/14 분기에서 초과** (각 p = 0.0001). 예외가 한 분기도 없다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   다음 분기 수익률 표준편차도 **고 그룹이 저 그룹의 2.26배**이고, 13/14 분기에서 그렇다 (p = 0.0018).</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>⇒ **변동성 그룹은 다음 분기에 '어디로 갈지' 는 못 맞히지만 '얼마나 멀리 갈지' 는 아주 잘 맞힌다.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   고변동 그룹은 다음 분기에도 양 끝(상·하)으로 벌어지고, 저변동 그룹은 가운데로 몰린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ※ 이건 놀라운 결과가 아니다 — 변동성 지속성(§10-5)을 '다음 분기 수익률의 퍼짐' 이라는 실용적 형태로 다시 말한 것이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>⇒ **쓸모의 방향이 정해진다.** 이 그룹은 종목 고르기(알파)가 아니라 **위험 예산·포지션 사이징**에 쓰는 것이 맞다 —</t>
+          <t xml:space="preserve">   **고 그룹은 14/14 분기에서 33.3% 미만, 저 그룹은 14/14 분기에서 초과** (각 p = 0.0001). 예외가 한 분기도 없다.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   다음 분기 수익률 표준편차도 **고 그룹이 저 그룹의 2.26배**이고, 13/14 분기에서 그렇다 (p = 0.0018).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>⇒ **변동성 그룹은 다음 분기에 '어디로 갈지' 는 못 맞히지만 '얼마나 멀리 갈지' 는 아주 잘 맞힌다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   고변동 그룹은 다음 분기에도 양 끝(상·하)으로 벌어지고, 저변동 그룹은 가운데로 몰린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 이건 놀라운 결과가 아니다 — 변동성 지속성(§10-5)을 '다음 분기 수익률의 퍼짐' 이라는 실용적 형태로 다시 말한 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>⇒ **쓸모의 방향이 정해진다.** 이 그룹은 종목 고르기(알파)가 아니라 **위험 예산·포지션 사이징**에 쓰는 것이 맞다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   같은 금액을 넣어도 고 그룹은 저 그룹의 2.26배로 흔들린다는 뜻이니까.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>⚠ 다만 '어느 쪽으로' 흔들릴지는 이 표가 말해주지 않는다. 손실 쪽도 그만큼 넓다.</t>
         </is>

--- a/docs/holdtiming/results/YZ그룹_분기예측.xlsx
+++ b/docs/holdtiming/results/YZ그룹_분기예측.xlsx
@@ -1558,7 +1558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1585,954 +1585,1077 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>분할은 **균등 3분할(1/3 : 1/3 : 1/3)** 이다 — 3:4:3 이 아니다. 두 축 모두 `rank(pct) ≤ 1/3, ≤ 2/3` 로 자른다.</t>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>◆ 이 표를 읽는 법 — 첫 행(변동성 高 · 전분기수익 上)으로</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   실측 축 비율 — 변동성 저 33.2% / 중 33.3% / 고 33.6%   ·   수익률 하 33.1% / 중 33.3% / 상 33.6%</t>
+          <t xml:space="preserve">   **한 행 = 한 셀.** 매 분기 전 종목을 (전분기 변동성 3등분) × (전분기 수익률 3등분) 으로 9칸에 나눠 담고, 14분기치를 쌓은 것이다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   분기당 판정 종목 193~206종목 (중앙 201).</t>
-        </is>
-      </c>
+      <c r="A6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>⚠ **축은 균등한데 9셀은 전혀 균등하지 않다.** 두 축이 독립이면 각 셀이 11.1% 여야 하는데 실제는 4.9%~18.5% 다 —</t>
+          <t xml:space="preserve">   **n합계 519** — 14분기 동안 이 칸에 들어간 **종목-분기 관측 수**. 한 종목이 여러 분기에 반복 등장한다(같은 종목을 여러 번 센 값이다).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   **전체 대비 18.5% · n평균 37.1** — 분기마다 평균 37종목이 이 칸에 있었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **→다음분기 上 / 中 / 下** = 이 칸의 종목들이 **다음 분기** 수익률 3등분에서 어디로 갔나. **세 값의 합은 항상 100%** 다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      36.2 / 25.3 / 38.5 → 다음 분기에 상위 36.2%, 중위 25.3%, 하위 38.5% 로 흩어졌다는 뜻. 무작위면 33.3 / 33.3 / 33.3 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ⚠ 上(36.2)보다 下(38.5)가 크지만 **차이 2.3%p 는 잡음 범위**다(부호검정 p=0.791). 정작 눈에 띄는 건 **中이 25.3 으로 낮은 것**이고,</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        그게 '가운데를 비우고 양 끝으로 벌어진다' = 아래 ② 산포 결과다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **다음분기 순위백분위 49.2%** — 이 칸 종목들의 **다음 분기 수익률 등수**를 그 분기 전체(약 200종목) 기준 백분위로 바꿔 평균낸 값.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      100% = 그 분기 1등, 0% = 꼴찌, **50% = 딱 중간(무작위와 같음)**. 49.2% 는 사실상 50% 다. 위 上/中/下 를 연속값 하나로 요약한 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **부호검정 p 0.791** — '이 칸이 다음 분기에 평균보다 잘하나' 를 **분기를 단위로** 검정한 값이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      14분기 각각에서 이 칸의 순위백분위 평균을 구해 50%를 넘은 분기를 세니 **6/14**. 동전던지기(7/14)와 다르다고 할 수 없어 p=0.791.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ⚠ 종목 519개를 표본으로 세지 **않는다** — 같은 분기 종목들은 시장을 함께 타므로 독립이 아니다(유사반복).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   실례 — 2025Q4 로 그룹을 짜고 2026Q1 을 본 분기: 이 칸에 44종목이 있었고 上 18 / 中 14 / 下 12 종목으로 갈렸다(순위백분위 평균 54.7%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      같은 칸 안에서 성호전자 +249.5%(순위 99.0%) 와 하이젠알앤엠 −41.2%(순위 0.5%) 가 함께 나왔다 — **한 칸이 이만큼 넓다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>분할은 **균등 3분할(1/3 : 1/3 : 1/3)** 이다 — 3:4:3 이 아니다. 두 축 모두 `rank(pct) ≤ 1/3, ≤ 2/3` 로 자른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   실측 축 비율 — 변동성 저 33.2% / 중 33.3% / 고 33.6%   ·   수익률 하 33.1% / 중 33.3% / 상 33.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   분기당 판정 종목 193~206종목 (중앙 201).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>⚠ **축은 균등한데 9셀은 전혀 균등하지 않다.** 두 축이 독립이면 각 셀이 11.1% 여야 하는데 실제는 4.9%~18.5% 다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">   변동성이 큰 종목이 수익률 극단으로도 가기 때문이다. **셀 크기의 불균등 자체가 아래 ② 산포 결과와 같은 현상이다.**</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>① 통합 — 9셀이 다음 분기 어디로 가나 (%). 무작위면 각 33.3</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>변동성</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>전분기 수익</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>n합계</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>전체 대비</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>분기수</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>n평균</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>n최소</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>n최대</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>→다음분기 上</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>→다음분기 中</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>→다음분기 下</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 순위백분위</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="C34" s="19" t="n">
+        <v>519</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>0.1854233654876742</v>
+      </c>
+      <c r="E34" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F34" s="21" t="n">
+        <v>37.07142857142857</v>
+      </c>
+      <c r="G34" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="I34" s="20" t="n">
+        <v>0.3621145527131203</v>
+      </c>
+      <c r="J34" s="20" t="n">
+        <v>0.2525037785127389</v>
+      </c>
+      <c r="K34" s="20" t="n">
+        <v>0.3853816687741408</v>
+      </c>
+      <c r="L34" s="20" t="n">
+        <v>0.4918092662045903</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
         <is>
           <t>중</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="C35" s="19" t="n">
+        <v>193</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>0.06895319757056091</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>13.78571428571429</v>
+      </c>
+      <c r="G35" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v>0.3829871983758539</v>
+      </c>
+      <c r="J35" s="20" t="n">
+        <v>0.2455020644621485</v>
+      </c>
+      <c r="K35" s="20" t="n">
+        <v>0.3715107371619976</v>
+      </c>
+      <c r="L35" s="20" t="n">
+        <v>0.5165471690413012</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>하</t>
         </is>
       </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>순위백분위</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>고</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="C36" s="7" t="n">
+        <v>228</v>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>0.08145766345123258</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F36" s="23" t="n">
+        <v>16.28571428571428</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="I36" s="22" t="n">
+        <v>0.381878124210057</v>
+      </c>
+      <c r="J36" s="22" t="n">
+        <v>0.2461880626376425</v>
+      </c>
+      <c r="K36" s="22" t="n">
+        <v>0.3719338131523006</v>
+      </c>
+      <c r="L36" s="22" t="n">
+        <v>0.5153359590705595</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>상</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
-        <v>519</v>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>0.1854233654876742</v>
-      </c>
-      <c r="E13" s="19" t="n">
+      <c r="C37" s="19" t="n">
+        <v>283</v>
+      </c>
+      <c r="D37" s="20" t="n">
+        <v>0.1011075384065738</v>
+      </c>
+      <c r="E37" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="F13" s="21" t="n">
-        <v>37.07142857142857</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>19</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>0.3621145527131203</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>0.2525037785127389</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0.3853816687741408</v>
-      </c>
-      <c r="L13" s="20" t="n">
+      <c r="F37" s="21" t="n">
+        <v>20.21428571428572</v>
+      </c>
+      <c r="G37" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I37" s="20" t="n">
+        <v>0.3321685821891339</v>
+      </c>
+      <c r="J37" s="20" t="n">
+        <v>0.3054112455258783</v>
+      </c>
+      <c r="K37" s="20" t="n">
+        <v>0.3624201722849878</v>
+      </c>
+      <c r="L37" s="20" t="n">
+        <v>0.4846002478873672</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C38" s="19" t="n">
+        <v>309</v>
+      </c>
+      <c r="D38" s="20" t="n">
+        <v>0.1103965702036442</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F38" s="21" t="n">
+        <v>22.07142857142857</v>
+      </c>
+      <c r="G38" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="I38" s="20" t="n">
+        <v>0.330062388545553</v>
+      </c>
+      <c r="J38" s="20" t="n">
+        <v>0.321381351930551</v>
+      </c>
+      <c r="K38" s="20" t="n">
+        <v>0.348556259523896</v>
+      </c>
+      <c r="L38" s="20" t="n">
+        <v>0.4904441505333949</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>340</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0.1214719542693819</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F39" s="23" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="22" t="n">
+        <v>0.354044771104571</v>
+      </c>
+      <c r="J39" s="22" t="n">
+        <v>0.2887325231305552</v>
+      </c>
+      <c r="K39" s="22" t="n">
+        <v>0.3572227057648737</v>
+      </c>
+      <c r="L39" s="22" t="n">
+        <v>0.4941591577026377</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="25" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C40" s="19" t="n">
+        <v>136</v>
+      </c>
+      <c r="D40" s="20" t="n">
+        <v>0.04858878170775277</v>
+      </c>
+      <c r="E40" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F40" s="21" t="n">
+        <v>10.46153846153846</v>
+      </c>
+      <c r="G40" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="I40" s="20" t="n">
+        <v>0.2830830557074901</v>
+      </c>
+      <c r="J40" s="20" t="n">
+        <v>0.4204540557481734</v>
+      </c>
+      <c r="K40" s="20" t="n">
+        <v>0.2964628885443365</v>
+      </c>
+      <c r="L40" s="20" t="n">
+        <v>0.4870690618271913</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B41" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C41" s="19" t="n">
+        <v>431</v>
+      </c>
+      <c r="D41" s="20" t="n">
+        <v>0.1539835655591283</v>
+      </c>
+      <c r="E41" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>30.78571428571428</v>
+      </c>
+      <c r="G41" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="I41" s="20" t="n">
+        <v>0.2609409610104242</v>
+      </c>
+      <c r="J41" s="20" t="n">
+        <v>0.5098482740679136</v>
+      </c>
+      <c r="K41" s="20" t="n">
+        <v>0.2292107649216622</v>
+      </c>
+      <c r="L41" s="20" t="n">
+        <v>0.5214860595918006</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0.1286173633440514</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="I42" s="22" t="n">
+        <v>0.3200885761154733</v>
+      </c>
+      <c r="J42" s="22" t="n">
+        <v>0.3922113064848045</v>
+      </c>
+      <c r="K42" s="22" t="n">
+        <v>0.2877001173997222</v>
+      </c>
+      <c r="L42" s="22" t="n">
+        <v>0.5060483126881633</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   n합계 = 14분기 누적 셀-분기 종목 수 (총 2,799). ⚠ 셀-분기 표본이 5종목 미만이면 그 분기는 제외했다 — 실측 최소가 2종목까지 내려가는데 그런 분기의 비율은 잡음이다(저·상 이 1개 분기 빠져 13분기).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>② 셀별 부호검정 — 분기를 단위로 (종목이 아니다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>셀</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>순위백분위&gt;50% 인 분기</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>평균 순위백분위</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>부호검정 p</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="27" t="inlineStr">
+        <is>
+          <t>변동성 고 · 전분기수익 상</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="n">
         <v>0.4918092662045903</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>고</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>193</v>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>0.06895319757056091</v>
-      </c>
-      <c r="E14" s="19" t="n">
+      <c r="E48" s="28" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>변동성 고 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="F14" s="21" t="n">
-        <v>13.78571428571429</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>21</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>0.3829871983758539</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>0.2455020644621485</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>0.3715107371619976</v>
-      </c>
-      <c r="L14" s="20" t="n">
-        <v>0.5165471690413012</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>고</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>228</v>
-      </c>
-      <c r="D15" s="22" t="n">
-        <v>0.08145766345123258</v>
-      </c>
-      <c r="E15" s="7" t="n">
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>0.516547169041301</v>
+      </c>
+      <c r="E49" s="28" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>변동성 고 · 전분기수익 하</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="F15" s="23" t="n">
-        <v>16.28571428571428</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="I15" s="22" t="n">
-        <v>0.381878124210057</v>
-      </c>
-      <c r="J15" s="22" t="n">
-        <v>0.2461880626376425</v>
-      </c>
-      <c r="K15" s="22" t="n">
-        <v>0.3719338131523006</v>
-      </c>
-      <c r="L15" s="22" t="n">
-        <v>0.5153359590705595</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="n">
-        <v>283</v>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>0.1011075384065738</v>
-      </c>
-      <c r="E16" s="19" t="n">
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>0.5153359590705594</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 상</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="F16" s="21" t="n">
-        <v>20.21428571428572</v>
-      </c>
-      <c r="G16" s="19" t="n">
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="n">
+        <v>0.4846002478873672</v>
+      </c>
+      <c r="E51" s="28" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="H16" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>0.3321685821891339</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <v>0.3054112455258783</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>0.3624201722849878</v>
-      </c>
-      <c r="L16" s="20" t="n">
-        <v>0.4846002478873672</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="n">
-        <v>309</v>
-      </c>
-      <c r="D17" s="20" t="n">
-        <v>0.1103965702036442</v>
-      </c>
-      <c r="E17" s="19" t="n">
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="n">
+        <v>0.4904441505333949</v>
+      </c>
+      <c r="E52" s="28" t="n">
+        <v>0.1795654296875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>변동성 중 · 전분기수익 하</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="F17" s="21" t="n">
-        <v>22.07142857142857</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>28</v>
-      </c>
-      <c r="I17" s="20" t="n">
-        <v>0.330062388545553</v>
-      </c>
-      <c r="J17" s="20" t="n">
-        <v>0.321381351930551</v>
-      </c>
-      <c r="K17" s="20" t="n">
-        <v>0.348556259523896</v>
-      </c>
-      <c r="L17" s="20" t="n">
-        <v>0.4904441505333949</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>340</v>
-      </c>
-      <c r="D18" s="22" t="n">
-        <v>0.1214719542693819</v>
-      </c>
-      <c r="E18" s="7" t="n">
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>0.4941591577026377</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="27" t="inlineStr">
+        <is>
+          <t>변동성 저 · 전분기수익 상</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>5/13</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="n">
+        <v>0.4870690618271913</v>
+      </c>
+      <c r="E54" s="28" t="n">
+        <v>0.5810546875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>변동성 저 · 전분기수익 중</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="F18" s="23" t="n">
-        <v>24.28571428571428</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="22" t="n">
-        <v>0.354044771104571</v>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>0.2887325231305552</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>0.3572227057648737</v>
-      </c>
-      <c r="L18" s="22" t="n">
-        <v>0.4941591577026377</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>저</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>136</v>
-      </c>
-      <c r="D19" s="20" t="n">
-        <v>0.04858878170775277</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>10.46153846153846</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>26</v>
-      </c>
-      <c r="I19" s="20" t="n">
-        <v>0.2830830557074901</v>
-      </c>
-      <c r="J19" s="20" t="n">
-        <v>0.4204540557481734</v>
-      </c>
-      <c r="K19" s="20" t="n">
-        <v>0.2964628885443365</v>
-      </c>
-      <c r="L19" s="20" t="n">
-        <v>0.4870690618271913</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>저</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>431</v>
-      </c>
-      <c r="D20" s="20" t="n">
-        <v>0.1539835655591283</v>
-      </c>
-      <c r="E20" s="19" t="n">
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="n">
+        <v>0.5214860595918006</v>
+      </c>
+      <c r="E55" s="28" t="n">
+        <v>0.79052734375</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>변동성 저 · 전분기수익 하</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="F20" s="21" t="n">
-        <v>30.78571428571428</v>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>24</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>37</v>
-      </c>
-      <c r="I20" s="20" t="n">
-        <v>0.2609409610104242</v>
-      </c>
-      <c r="J20" s="20" t="n">
-        <v>0.5098482740679136</v>
-      </c>
-      <c r="K20" s="20" t="n">
-        <v>0.2292107649216622</v>
-      </c>
-      <c r="L20" s="20" t="n">
-        <v>0.5214860595918006</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>저</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>360</v>
-      </c>
-      <c r="D21" s="22" t="n">
-        <v>0.1286173633440514</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="F21" s="23" t="n">
-        <v>25.71428571428572</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="I21" s="22" t="n">
-        <v>0.3200885761154733</v>
-      </c>
-      <c r="J21" s="22" t="n">
-        <v>0.3922113064848045</v>
-      </c>
-      <c r="K21" s="22" t="n">
-        <v>0.2877001173997222</v>
-      </c>
-      <c r="L21" s="22" t="n">
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="n">
         <v>0.5060483126881633</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   n합계 = 14분기 누적 셀-분기 종목 수 (총 2,799). ⚠ 셀-분기 표본이 5종목 미만이면 그 분기는 제외했다 — 실측 최소가 2종목까지 내려가는데 그런 분기의 비율은 잡음이다(저·상 이 1개 분기 빠져 13분기).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>② 셀별 부호검정 — 분기를 단위로 (종목이 아니다)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>셀</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>분기</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>순위&gt;0.5</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>평균 순위백분위</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>부호검정 p</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="27" t="inlineStr">
-        <is>
-          <t>변동성 고 · 전분기수익 상</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>6/14</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="n">
-        <v>0.4918092662045903</v>
-      </c>
-      <c r="E27" s="28" t="n">
-        <v>0.79052734375</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>변동성 고 · 전분기수익 중</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>8/14</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="n">
-        <v>0.516547169041301</v>
-      </c>
-      <c r="E28" s="28" t="n">
-        <v>0.79052734375</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>변동성 고 · 전분기수익 하</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>7/14</t>
-        </is>
-      </c>
-      <c r="D29" s="22" t="n">
-        <v>0.5153359590705594</v>
-      </c>
-      <c r="E29" s="13" t="n">
+      <c r="E56" s="13" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>변동성 중 · 전분기수익 상</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>6/14</t>
-        </is>
-      </c>
-      <c r="D30" s="20" t="n">
-        <v>0.4846002478873672</v>
-      </c>
-      <c r="E30" s="28" t="n">
-        <v>0.79052734375</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>변동성 중 · 전분기수익 중</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>4/14</t>
-        </is>
-      </c>
-      <c r="D31" s="20" t="n">
-        <v>0.4904441505333949</v>
-      </c>
-      <c r="E31" s="28" t="n">
-        <v>0.1795654296875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>변동성 중 · 전분기수익 하</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>7/14</t>
-        </is>
-      </c>
-      <c r="D32" s="22" t="n">
-        <v>0.4941591577026377</v>
-      </c>
-      <c r="E32" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>변동성 저 · 전분기수익 상</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>5/13</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="n">
-        <v>0.4870690618271913</v>
-      </c>
-      <c r="E33" s="28" t="n">
-        <v>0.5810546875</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="27" t="inlineStr">
-        <is>
-          <t>변동성 저 · 전분기수익 중</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C34" s="18" t="inlineStr">
-        <is>
-          <t>8/14</t>
-        </is>
-      </c>
-      <c r="D34" s="20" t="n">
-        <v>0.5214860595918006</v>
-      </c>
-      <c r="E34" s="28" t="n">
-        <v>0.79052734375</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>변동성 저 · 전분기수익 하</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>7/14</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="n">
-        <v>0.5060483126881633</v>
-      </c>
-      <c r="E35" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>★ **9셀 어디에도 예측력이 없다.** 평균 순위백분위가 48.5~52.1% 로 전부 50% 근처이고, 부호검정 p 는 0.18~1.00 이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   셀이 9개라 다중비교다 — 본페로니 임계 p &lt; 0.0056. **근처에 온 셀조차 없다.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>★ **전분기 수익률 축은 아무 정보도 없다.** 같은 변동성 안에서 상/중/하의 다음 분기 분포가 거의 같다(예: 고변동에서 '상' 36.2 / '중' 38.3 / '하' 38.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⇒ **모멘텀도 반전도 없다.** 변동성으로 조건을 걸어도 마찬가지다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>③ ★ 그런데 '방향' 이 아니라 '산포' 는 아주 강하게 예측한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>변동성</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>분기</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>다음분기 '중간' 비율</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>'중간' &lt; 33.3% 인 분기</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>'중간' &gt; 33.3% 인 분기</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>p(치우침)</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>다음분기 수익률 sd</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>sd / 시장sd</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>고</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C45" s="22" t="n">
-        <v>0.2423371309379249</v>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>14/14</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>0/14</t>
-        </is>
-      </c>
-      <c r="F45" s="29" t="n">
-        <v>0.0001220703125</v>
-      </c>
-      <c r="G45" s="22" t="n">
-        <v>0.3591701874901823</v>
-      </c>
-      <c r="H45" s="11" t="n">
-        <v>1.241659688105479</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="14" t="inlineStr">
-        <is>
-          <t>중</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C46" s="22" t="n">
-        <v>0.3025511806199361</v>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>10/14</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>2/14</t>
-        </is>
-      </c>
-      <c r="F46" s="29" t="n">
-        <v>0.012939453125</v>
-      </c>
-      <c r="G46" s="22" t="n">
-        <v>0.2505778672840408</v>
-      </c>
-      <c r="H46" s="11" t="n">
-        <v>0.9545662061401605</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>저</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C47" s="22" t="n">
-        <v>0.4544587523063709</v>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>0/14</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>14/14</t>
-        </is>
-      </c>
-      <c r="F47" s="29" t="n">
-        <v>0.0001220703125</v>
-      </c>
-      <c r="G47" s="22" t="n">
-        <v>0.1465956287972339</v>
-      </c>
-      <c r="H47" s="11" t="n">
-        <v>0.5541064528533126</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   무작위면 '중간' 비율이 33.3% 여야 한다. 실측은 **고 24.2% / 중 30.3% / 저 45.4%** 다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   **고 그룹은 14/14 분기에서 33.3% 미만, 저 그룹은 14/14 분기에서 초과** (각 p = 0.0001). 예외가 한 분기도 없다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   다음 분기 수익률 표준편차도 **고 그룹이 저 그룹의 2.26배**이고, 13/14 분기에서 그렇다 (p = 0.0018).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>⇒ **변동성 그룹은 다음 분기에 '어디로 갈지' 는 못 맞히지만 '얼마나 멀리 갈지' 는 아주 잘 맞힌다.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   고변동 그룹은 다음 분기에도 양 끝(상·하)으로 벌어지고, 저변동 그룹은 가운데로 몰린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ※ 이건 놀라운 결과가 아니다 — 변동성 지속성(§10-5)을 '다음 분기 수익률의 퍼짐' 이라는 실용적 형태로 다시 말한 것이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>⇒ **쓸모의 방향이 정해진다.** 이 그룹은 종목 고르기(알파)가 아니라 **위험 예산·포지션 사이징**에 쓰는 것이 맞다 —</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   같은 금액을 넣어도 고 그룹은 저 그룹의 2.26배로 흔들린다는 뜻이니까.</t>
-        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>★ **9셀 어디에도 예측력이 없다.** 평균 순위백분위가 48.5~52.1% 로 전부 50% 근처이고, 부호검정 p 는 0.18~1.00 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   셀이 9개라 다중비교다 — 본페로니 임계 p &lt; 0.0056. **근처에 온 셀조차 없다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>★ **전분기 수익률 축은 아무 정보도 없다.** 같은 변동성 안에서 상/중/하의 다음 분기 분포가 거의 같다(예: 고변동에서 '상' 36.2 / '중' 38.3 / '하' 38.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **모멘텀도 반전도 없다.** 변동성으로 조건을 걸어도 마찬가지다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>③ ★ 그런데 '방향' 이 아니라 '산포' 는 아주 강하게 예측한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>변동성</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 '중간' 비율</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>'중간' &lt; 33.3% 인 분기</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>'중간' &gt; 33.3% 인 분기</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>p(치우침)</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 수익률 sd</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>sd / 시장sd</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C66" s="22" t="n">
+        <v>0.2423371309379249</v>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>0/14</t>
+        </is>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>0.0001220703125</v>
+      </c>
+      <c r="G66" s="22" t="n">
+        <v>0.3591701874901823</v>
+      </c>
+      <c r="H66" s="11" t="n">
+        <v>1.241659688105479</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C67" s="22" t="n">
+        <v>0.3025511806199361</v>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+      <c r="F67" s="29" t="n">
+        <v>0.012939453125</v>
+      </c>
+      <c r="G67" s="22" t="n">
+        <v>0.2505778672840408</v>
+      </c>
+      <c r="H67" s="11" t="n">
+        <v>0.9545662061401605</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C68" s="22" t="n">
+        <v>0.4544587523063709</v>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>0/14</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="n">
+        <v>0.0001220703125</v>
+      </c>
+      <c r="G68" s="22" t="n">
+        <v>0.1465956287972339</v>
+      </c>
+      <c r="H68" s="11" t="n">
+        <v>0.5541064528533126</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   무작위면 '중간' 비율이 33.3% 여야 한다. 실측은 **고 24.2% / 중 30.3% / 저 45.4%** 다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **고 그룹은 14/14 분기에서 33.3% 미만, 저 그룹은 14/14 분기에서 초과** (각 p = 0.0001). 예외가 한 분기도 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   다음 분기 수익률 표준편차도 **고 그룹이 저 그룹의 2.26배**이고, 13/14 분기에서 그렇다 (p = 0.0018).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>⇒ **변동성 그룹은 다음 분기에 '어디로 갈지' 는 못 맞히지만 '얼마나 멀리 갈지' 는 아주 잘 맞힌다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   고변동 그룹은 다음 분기에도 양 끝(상·하)으로 벌어지고, 저변동 그룹은 가운데로 몰린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 이건 놀라운 결과가 아니다 — 변동성 지속성(§10-5)을 '다음 분기 수익률의 퍼짐' 이라는 실용적 형태로 다시 말한 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>⇒ **쓸모의 방향이 정해진다.** 이 그룹은 종목 고르기(알파)가 아니라 **위험 예산·포지션 사이징**에 쓰는 것이 맞다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   같은 금액을 넣어도 고 그룹은 저 그룹의 2.26배로 흔들린다는 뜻이니까.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>⚠ 다만 '어느 쪽으로' 흔들릴지는 이 표가 말해주지 않는다. 손실 쪽도 그만큼 넓다.</t>
         </is>

--- a/docs/holdtiming/results/YZ그룹_분기예측.xlsx
+++ b/docs/holdtiming/results/YZ그룹_분기예측.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기_패널" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="베타_알파" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9셀_전이" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9셀_수익률원값" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +99,12 @@
       <color rgb="FF6D4C41"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -146,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,6 +231,16 @@
     </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -636,7 +653,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>⚠ 시장 기준은 **동일가중(전 종목 중앙)** 이다. BM(102110)은 시총가중이라 소수 대형주에 끌린다 — 동일가중과의 상관이 **+0.295** 뿐이고,</t>
+          <t>⚠ 시장 기준은 **동일가중(전 종목 중앙)** 이다. BM(102110)은 시총가중이라 소수 대형주에 끌린다 — 동일가중과의 상관이 **+0.286** 뿐이고,</t>
         </is>
       </c>
     </row>
@@ -1179,28 +1196,28 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="7" t="n">
         <v>206</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-0.07468734968734969</v>
+        <v>-0.06317879007400462</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>-0.1630677587490692</v>
+        <v>-0.1649292628443783</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>-0.1548913043478261</v>
+        <v>-0.1522781774580336</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>-0.09904534606205251</v>
+        <v>-0.1050119331742243</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>0.03148325358851678</v>
+        <v>0.03087774294670853</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>-0.1863745579363428</v>
+        <v>-0.1831559204047422</v>
       </c>
     </row>
     <row r="25">
@@ -1213,7 +1230,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   고−저 스프레드 중앙 -0.11% · 평균 +0.06% — 0 근처다.</t>
+          <t xml:space="preserve">   고−저 스프레드 중앙 -0.11% · 평균 +0.08% — 0 근처다.</t>
         </is>
       </c>
     </row>
@@ -1301,13 +1318,13 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1.177017786485905</v>
+        <v>1.180396478077235</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>-0.0006420913930472173</v>
+        <v>-0.001537109293620727</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.8370060087571247</v>
+        <v>0.8253678674097469</v>
       </c>
     </row>
     <row r="6">
@@ -1317,13 +1334,13 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>1.085724016666886</v>
+        <v>1.104471303979591</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>-0.005364374120372576</v>
+        <v>-0.007316250669927794</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.8571068446181377</v>
+        <v>0.8529227899431059</v>
       </c>
     </row>
     <row r="7">
@@ -1333,13 +1350,13 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>0.8012151585676585</v>
+        <v>0.8225864249292379</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>0.01116014937205734</v>
+        <v>0.009736460515295371</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.7405288725374739</v>
+        <v>0.760087937191971</v>
       </c>
     </row>
     <row r="9">
@@ -1383,7 +1400,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   시장수익률 × 고−저 상관 +0.364</t>
+          <t xml:space="preserve">   시장수익률 × 고−저 상관 +0.344</t>
         </is>
       </c>
     </row>
@@ -1486,10 +1503,10 @@
         <v>-0.001111399858525097</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1.177017786485905</v>
+        <v>1.180396478077235</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.8012151585676585</v>
+        <v>0.8225864249292379</v>
       </c>
     </row>
     <row r="27">
@@ -1513,10 +1530,10 @@
         <v>-0.01236248592110645</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1.113214536164547</v>
+        <v>1.124190280503157</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.8061447168126685</v>
+        <v>0.8346016227950216</v>
       </c>
     </row>
     <row r="28">
@@ -1841,16 +1858,16 @@
         <v>46</v>
       </c>
       <c r="I34" s="20" t="n">
-        <v>0.3621145527131203</v>
+        <v>0.3636673477441762</v>
       </c>
       <c r="J34" s="20" t="n">
         <v>0.2525037785127389</v>
       </c>
       <c r="K34" s="20" t="n">
-        <v>0.3853816687741408</v>
+        <v>0.3838288737430849</v>
       </c>
       <c r="L34" s="20" t="n">
-        <v>0.4918092662045903</v>
+        <v>0.4921183176428102</v>
       </c>
     </row>
     <row r="35">
@@ -1883,16 +1900,16 @@
         <v>21</v>
       </c>
       <c r="I35" s="20" t="n">
-        <v>0.3829871983758539</v>
+        <v>0.390130055518711</v>
       </c>
       <c r="J35" s="20" t="n">
-        <v>0.2455020644621485</v>
+        <v>0.2383592073192914</v>
       </c>
       <c r="K35" s="20" t="n">
         <v>0.3715107371619976</v>
       </c>
       <c r="L35" s="20" t="n">
-        <v>0.5165471690413012</v>
+        <v>0.5169632578069044</v>
       </c>
     </row>
     <row r="36">
@@ -1934,7 +1951,7 @@
         <v>0.3719338131523006</v>
       </c>
       <c r="L36" s="22" t="n">
-        <v>0.5153359590705595</v>
+        <v>0.5160027679897956</v>
       </c>
     </row>
     <row r="37">
@@ -1967,16 +1984,16 @@
         <v>28</v>
       </c>
       <c r="I37" s="20" t="n">
-        <v>0.3321685821891339</v>
+        <v>0.327966901516865</v>
       </c>
       <c r="J37" s="20" t="n">
-        <v>0.3054112455258783</v>
+        <v>0.3096129261981472</v>
       </c>
       <c r="K37" s="20" t="n">
         <v>0.3624201722849878</v>
       </c>
       <c r="L37" s="20" t="n">
-        <v>0.4846002478873672</v>
+        <v>0.4853549186877261</v>
       </c>
     </row>
     <row r="38">
@@ -2009,16 +2026,16 @@
         <v>28</v>
       </c>
       <c r="I38" s="20" t="n">
-        <v>0.330062388545553</v>
+        <v>0.3270861980693625</v>
       </c>
       <c r="J38" s="20" t="n">
-        <v>0.321381351930551</v>
+        <v>0.3243575424067415</v>
       </c>
       <c r="K38" s="20" t="n">
         <v>0.348556259523896</v>
       </c>
       <c r="L38" s="20" t="n">
-        <v>0.4904441505333949</v>
+        <v>0.4898806969966404</v>
       </c>
     </row>
     <row r="39">
@@ -2054,13 +2071,13 @@
         <v>0.354044771104571</v>
       </c>
       <c r="J39" s="22" t="n">
-        <v>0.2887325231305552</v>
+        <v>0.2861815027223919</v>
       </c>
       <c r="K39" s="22" t="n">
-        <v>0.3572227057648737</v>
+        <v>0.359773726173037</v>
       </c>
       <c r="L39" s="22" t="n">
-        <v>0.4941591577026377</v>
+        <v>0.4937257319051342</v>
       </c>
     </row>
     <row r="40">
@@ -2093,16 +2110,16 @@
         <v>26</v>
       </c>
       <c r="I40" s="20" t="n">
-        <v>0.2830830557074901</v>
+        <v>0.2702625428869773</v>
       </c>
       <c r="J40" s="20" t="n">
-        <v>0.4204540557481734</v>
+        <v>0.4332745685686862</v>
       </c>
       <c r="K40" s="20" t="n">
         <v>0.2964628885443365</v>
       </c>
       <c r="L40" s="20" t="n">
-        <v>0.4870690618271913</v>
+        <v>0.486073293841132</v>
       </c>
     </row>
     <row r="41">
@@ -2135,16 +2152,16 @@
         <v>37</v>
       </c>
       <c r="I41" s="20" t="n">
-        <v>0.2609409610104242</v>
+        <v>0.2589001446838937</v>
       </c>
       <c r="J41" s="20" t="n">
-        <v>0.5098482740679136</v>
+        <v>0.5118890903944442</v>
       </c>
       <c r="K41" s="20" t="n">
         <v>0.2292107649216622</v>
       </c>
       <c r="L41" s="20" t="n">
-        <v>0.5214860595918006</v>
+        <v>0.5212681083336275</v>
       </c>
     </row>
     <row r="42">
@@ -2177,16 +2194,16 @@
         <v>42</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>0.3200885761154733</v>
+        <v>0.3253795814064785</v>
       </c>
       <c r="J42" s="22" t="n">
-        <v>0.3922113064848045</v>
+        <v>0.3869203011937992</v>
       </c>
       <c r="K42" s="22" t="n">
         <v>0.2877001173997222</v>
       </c>
       <c r="L42" s="22" t="n">
-        <v>0.5060483126881633</v>
+        <v>0.5060097859506074</v>
       </c>
     </row>
     <row r="43">
@@ -2245,7 +2262,7 @@
         </is>
       </c>
       <c r="D48" s="20" t="n">
-        <v>0.4918092662045903</v>
+        <v>0.4921183176428102</v>
       </c>
       <c r="E48" s="28" t="n">
         <v>0.79052734375</v>
@@ -2266,7 +2283,7 @@
         </is>
       </c>
       <c r="D49" s="20" t="n">
-        <v>0.516547169041301</v>
+        <v>0.5169632578069044</v>
       </c>
       <c r="E49" s="28" t="n">
         <v>0.79052734375</v>
@@ -2287,7 +2304,7 @@
         </is>
       </c>
       <c r="D50" s="22" t="n">
-        <v>0.5153359590705594</v>
+        <v>0.5160027679897955</v>
       </c>
       <c r="E50" s="13" t="n">
         <v>1</v>
@@ -2308,7 +2325,7 @@
         </is>
       </c>
       <c r="D51" s="20" t="n">
-        <v>0.4846002478873672</v>
+        <v>0.4853549186877262</v>
       </c>
       <c r="E51" s="28" t="n">
         <v>0.79052734375</v>
@@ -2329,7 +2346,7 @@
         </is>
       </c>
       <c r="D52" s="20" t="n">
-        <v>0.4904441505333949</v>
+        <v>0.4898806969966403</v>
       </c>
       <c r="E52" s="28" t="n">
         <v>0.1795654296875</v>
@@ -2350,7 +2367,7 @@
         </is>
       </c>
       <c r="D53" s="22" t="n">
-        <v>0.4941591577026377</v>
+        <v>0.4937257319051342</v>
       </c>
       <c r="E53" s="13" t="n">
         <v>1</v>
@@ -2371,7 +2388,7 @@
         </is>
       </c>
       <c r="D54" s="20" t="n">
-        <v>0.4870690618271913</v>
+        <v>0.486073293841132</v>
       </c>
       <c r="E54" s="28" t="n">
         <v>0.5810546875</v>
@@ -2392,7 +2409,7 @@
         </is>
       </c>
       <c r="D55" s="20" t="n">
-        <v>0.5214860595918006</v>
+        <v>0.5212681083336275</v>
       </c>
       <c r="E55" s="28" t="n">
         <v>0.79052734375</v>
@@ -2413,7 +2430,7 @@
         </is>
       </c>
       <c r="D56" s="22" t="n">
-        <v>0.5060483126881633</v>
+        <v>0.5060097859506074</v>
       </c>
       <c r="E56" s="13" t="n">
         <v>1</v>
@@ -2506,7 +2523,7 @@
         <v>14</v>
       </c>
       <c r="C66" s="22" t="n">
-        <v>0.2423371309379249</v>
+        <v>0.2413019342505543</v>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
@@ -2538,7 +2555,7 @@
         <v>14</v>
       </c>
       <c r="C67" s="22" t="n">
-        <v>0.3025511806199361</v>
+        <v>0.3035863773073068</v>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
@@ -2547,17 +2564,17 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
       <c r="F67" s="29" t="n">
-        <v>0.012939453125</v>
+        <v>0.057373046875</v>
       </c>
       <c r="G67" s="22" t="n">
         <v>0.2505778672840408</v>
       </c>
       <c r="H67" s="11" t="n">
-        <v>0.9545662061401605</v>
+        <v>0.9501781789758886</v>
       </c>
     </row>
     <row r="68">
@@ -2658,6 +2675,774 @@
       <c r="A79" s="3" t="inlineStr">
         <is>
           <t>⚠ 다만 '어느 쪽으로' 흔들릴지는 이 표가 말해주지 않는다. 손실 쪽도 그만큼 넓다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>9셀의 다음 분기 수익률 — 중앙·평균·표본수</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>비율(上/中/下)·순위백분위로 바꾸지 않고 **수익률 그대로** 본다</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>① 실례 — 2025Q4 기준 9셀 → 2026Q1 수익률</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   전체 205종목 · 시장(동일가중) 중앙 +14.5% · 평균 +25.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>변동성</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>전분기 수익</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>표본</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 중앙</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 평균</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>평균−중앙</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>시장대비 중앙</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>0.1941185294035395</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>0.3116958930921637</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>0.1175773636886242</v>
+      </c>
+      <c r="G8" s="31" t="n">
+        <v>0.04893092744595373</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>0.3304498269896194</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>0.5575122694880211</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.2270624424984017</v>
+      </c>
+      <c r="G9" s="31" t="n">
+        <v>0.1852622250320337</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.09983765745723483</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0.2139248658457716</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>0.1140872083885368</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>-0.0453499445003509</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>0.2325092114959468</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>0.2254683412563766</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>-0.007040870239570257</v>
+      </c>
+      <c r="G11" s="31" t="n">
+        <v>0.0873216095383611</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>0.1590979269667794</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>0.1673164679385277</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>0.008218540971748317</v>
+      </c>
+      <c r="G12" s="31" t="n">
+        <v>0.01391032500919365</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>0.1033047387374669</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.3302149806607771</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>0.2269102419233102</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>-0.0418828632201188</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>0.08899297423887598</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>0.06238137150087895</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>-0.02661160273799703</v>
+      </c>
+      <c r="G14" s="32" t="n">
+        <v>-0.05619462771870976</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>0.1413276231263383</v>
+      </c>
+      <c r="E15" s="31" t="n">
+        <v>0.2416132443330372</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>0.1002856212066989</v>
+      </c>
+      <c r="G15" s="32" t="n">
+        <v>-0.003859978831247446</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>0.05335226530878701</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.08234151256107126</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>0.02898924725228426</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>-0.09183533664879873</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 한 분기라 셀이 얇다 — 저·상 5종목 · 고·하 8종목. 이 표는 '어떻게 읽는가' 의 예시이지 근거가 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>② 전 기간 — 분기쌍 14개를 모두 풀링 (셀-분기-종목 관측 2,801)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>변동성</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>전분기 수익</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>표본</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 중앙</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>다음분기 평균</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>평균−중앙</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>시장대비 중앙</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>시장대비 평균</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>519</v>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>0.02936630602782064</v>
+      </c>
+      <c r="E22" s="31" t="n">
+        <v>0.1158103706462649</v>
+      </c>
+      <c r="F22" s="20" t="n">
+        <v>0.08644406461844427</v>
+      </c>
+      <c r="G22" s="32" t="n">
+        <v>-0.01390454325932866</v>
+      </c>
+      <c r="H22" s="31" t="n">
+        <v>0.0809661734198118</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="n">
+        <v>193</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>0.04325259515570945</v>
+      </c>
+      <c r="E23" s="31" t="n">
+        <v>0.1986119701380208</v>
+      </c>
+      <c r="F23" s="20" t="n">
+        <v>0.1553593749823113</v>
+      </c>
+      <c r="G23" s="31" t="n">
+        <v>0.03545533686831481</v>
+      </c>
+      <c r="H23" s="31" t="n">
+        <v>0.1647530392690483</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>고</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>228</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>0.04517116300158697</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.1141813079989268</v>
+      </c>
+      <c r="F24" s="22" t="n">
+        <v>0.06901014499733979</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>0.007757126804425529</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>0.08162089819877036</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>283</v>
+      </c>
+      <c r="D25" s="31" t="n">
+        <v>0.03027522935779814</v>
+      </c>
+      <c r="E25" s="31" t="n">
+        <v>0.0833265100919115</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>0.05305128073411336</v>
+      </c>
+      <c r="G25" s="32" t="n">
+        <v>-0.009877940271011521</v>
+      </c>
+      <c r="H25" s="31" t="n">
+        <v>0.04716956358284894</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>309</v>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>0.01624883936861643</v>
+      </c>
+      <c r="E26" s="31" t="n">
+        <v>0.09054949586456575</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>0.07430065649594932</v>
+      </c>
+      <c r="G26" s="32" t="n">
+        <v>-0.009230384722061169</v>
+      </c>
+      <c r="H26" s="31" t="n">
+        <v>0.06083640452043106</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>340</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>0.02670781893004115</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.09810862372760616</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <v>0.07140080479756501</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>-0.001341056172006194</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>0.06237059185532282</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>138</v>
+      </c>
+      <c r="D28" s="31" t="n">
+        <v>0.01743694079023417</v>
+      </c>
+      <c r="E28" s="31" t="n">
+        <v>0.04553157103863418</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0.02809463024840001</v>
+      </c>
+      <c r="G28" s="31" t="n">
+        <v>0.0009388090002290794</v>
+      </c>
+      <c r="H28" s="31" t="n">
+        <v>0.01853062009600643</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="n">
+        <v>431</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>0.03838113554645028</v>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>0.07320162036533909</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0.0348204848188888</v>
+      </c>
+      <c r="G29" s="31" t="n">
+        <v>0.01017344837064194</v>
+      </c>
+      <c r="H29" s="31" t="n">
+        <v>0.036322935362699</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>저</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>360</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>0.02621348674883339</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>0.08040392610263368</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>0.05419043935380029</v>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>-0.01187949228409818</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>0.04711553714083148</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="n">
+        <v>2801</v>
+      </c>
+      <c r="D31" s="31" t="n">
+        <v>0.03183962264150941</v>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>0.09859615424815904</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0.06675653160664963</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="31" t="n">
+        <v>0.06460399363797537</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>읽기 — ⓐ **시장대비 중앙의 범위가 −1.4% ~ +3.5%p 로 매우 좁다.** 분기 수익률에서 이 정도 차이는 잡음 범위이고, 앞 시트의 부호검정도 전부 p &gt; 0.18 이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⓑ ★ **평균이 중앙보다 훨씬 크다** (전체 중앙 3.2% vs 평균 9.9%). 수익률 분포가 오른쪽으로 길게 꼬리를 끈다는 뜻이다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      소수의 대박이 평균을 끌어올린다. **평균만 보면 어느 셀이든 좋아 보인다** (시장대비 평균이 9셀 전부 양수인 것도 그래서다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⓒ ★ **평균−중앙 격차 자체가 변동성 그룹을 가른다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        고 그룹  +8.7 / +15.6 / +6.9%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        중 그룹  +5.3 / +7.5 / +7.1%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        저 그룹  +2.9 / +3.5 / +5.4%p</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      → 고변동 그룹일수록 오른쪽 꼬리가 길다. **이것이 앞 시트의 '산포' 결과를 수익률 원값으로 본 모습이다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⓓ 중앙으로 가장 높은 칸은 고·중(4.5%)이지만 표본 193개에 부호검정 p=0.791 이다 — **셀 하나를 골라 쓸 근거가 못 된다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 풀링이라 분기마다 다른 시장 수준이 섞여 있다 (2026Q2 는 시장 중앙 −4.8%, 2025Q2 는 +21.8%). '시장대비' 열은 그 분기 시장 중앙을 뺀 값이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>⚠ 같은 종목이 여러 분기에 반복 등장한다 — 표본 2,801 은 독립 관측 수가 아니다.</t>
         </is>
       </c>
     </row>
